--- a/MD/ПКФ.xlsx
+++ b/MD/ПКФ.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17771" windowHeight="9060"/>
+    <workbookView windowWidth="17771" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,7 @@
     <definedName name="ExternalData_4" localSheetId="0">Лист1!$Y$1:$Z$400</definedName>
     <definedName name="ExternalData_5" localSheetId="0">Лист1!$AE$1:$AF$100</definedName>
     <definedName name="ExternalData_6" localSheetId="0">Лист1!$AP$1:$AQ$400</definedName>
+    <definedName name="ExternalData_7" localSheetId="0">Лист1!$AT$1:$AU$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,21 +58,28 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" name="position" type="6" background="1" refreshedVersion="2" saveData="1">
+  <connection id="4" name="pkf3" type="6" background="1" refreshedVersion="2" saveData="1">
+    <textPr sourceFile="C:\Users\79159\Desktop\NNGU\ЧМ мага\MD\MD\pkf.txt">
+      <textFields>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="5" name="position" type="6" background="1" refreshedVersion="2" saveData="1">
     <textPr sourceFile="C:\Users\79159\Desktop\NNGU\ЧМ мага\MD\MD\position.txt">
       <textFields>
         <textField/>
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" name="position1" type="6" background="1" refreshedVersion="2" saveData="1">
+  <connection id="6" name="position1" type="6" background="1" refreshedVersion="2" saveData="1">
     <textPr sourceFile="C:\Users\79159\Desktop\NNGU\ЧМ мага\MD\MD\position.txt">
       <textFields>
         <textField/>
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" name="position2" type="6" background="1" refreshedVersion="2" saveData="1">
+  <connection id="7" name="position2" type="6" background="1" refreshedVersion="2" saveData="1">
     <textPr sourceFile="C:\Users\79159\Desktop\NNGU\ЧМ мага\MD\MD\position.txt">
       <textFields>
         <textField/>
@@ -82,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>165 К</t>
   </si>
@@ -91,6 +99,9 @@
   </si>
   <si>
     <t>150 K</t>
+  </si>
+  <si>
+    <t>100 К</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1036,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -12063,6 +12074,996 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0826052631578947"/>
+          <c:y val="0.16400462962963"/>
+          <c:w val="0.830552631578947"/>
+          <c:h val="0.691828703703704"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="smooth"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Лист1!$AT$1:$AT$400</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="400"/>
+                <c:pt idx="0">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.15</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.55</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.65</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.75</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.8</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.85</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.9</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.95</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.05</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.15</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2.25</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.35</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.45</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.55</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.6</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.65</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.7</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.75</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.85</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2.95</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3.05</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3.15</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3.35</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3.45</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3.55</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3.65</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.7</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>3.75</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3.8</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>3.85</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3.9</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3.95</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.05</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.1</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.15</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.35</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.4</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.55</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.6</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.65</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4.75</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.8</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.85</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>4.9</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.95</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Лист1!$AU$1:$AU$400</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="400"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.536777</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11.224612</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>14.642255</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.458753</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.379002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.91978</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.978874</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.583662</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.081257</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.065206</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.818914</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.975717</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.167136</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.772376</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.790493</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.411439</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.089478</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.365393</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.951487</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4.129426</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5.109711</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6.611051</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6.92324</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>5.900378</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6.366198</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.441533</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.195903</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.395305</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.221066</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.844471</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.586268</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.118138</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.973521</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.307926</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.754605</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4.083976</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>4.185186</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>4.745711</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.547284</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.249321</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.049053</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.017427</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.986855</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.583468</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.08269</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.294657</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.879402</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.770748</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3.279556</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2.850536</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2.995858</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3.552154</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.047083</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3.721087</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3.536777</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.491222</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4.860678</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.668545</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.188288</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.622097</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.570603</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4.593333</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4.695071</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.519214</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.580557</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>3.604955</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>3.562039</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2.883513</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>3.553227</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>3.841671</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.376761</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.005697</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.244132</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>3.742765</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.947643</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.278359</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.977825</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.327502</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.277289</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4.922318</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>3.865191</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>3.665387</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.456338</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="998791696"/>
+        <c:axId val="646085186"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="998791696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="5"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1400" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                  </a:rPr>
+                  <a:t>r/a</a:t>
+                </a:r>
+                <a:endParaRPr sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:uFillTx/>
+                  <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.919"/>
+              <c:y val="0.755092592592593"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ru-RU" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:uFill>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:uFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="646085186"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="646085186"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr defTabSz="914400">
+                  <a:defRPr lang="ru-RU" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1400" b="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                  </a:rPr>
+                  <a:t>g(r/a)</a:t>
+                </a:r>
+                <a:endParaRPr sz="1400" b="1">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:uFillTx/>
+                  <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.0115789473684211"/>
+              <c:y val="0.0302893518518518"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="ru-RU" sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:uFill>
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:uFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+Основной текст (восточно-азиат" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="998791696"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="ru-RU"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -12264,6 +13265,46 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -15501,6 +16542,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10190">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -15683,31 +17261,65 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>256540</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3159760" y="5494020"/>
+        <a:ext cx="4826000" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_7" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_6" connectionId="7" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_5" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_4" connectionId="6" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_3" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_2" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_3" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_4" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_5" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_6" connectionId="6" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15968,7 +17580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ400"/>
+  <dimension ref="A1:AU400"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.55555555555556" style="1" customWidth="1"/>
@@ -15980,9 +17592,11 @@
     <col min="31" max="31" width="5.66666666666667" customWidth="1"/>
     <col min="32" max="32" width="10.6666666666667" customWidth="1"/>
     <col min="42" max="43" width="10.6666666666667" customWidth="1"/>
+    <col min="46" max="46" width="5.66666666666667" customWidth="1"/>
+    <col min="47" max="47" width="10.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:47">
       <c r="A1" s="1">
         <v>0.05</v>
       </c>
@@ -16028,8 +17642,14 @@
       <c r="AQ1">
         <v>1.795634</v>
       </c>
-    </row>
-    <row r="2" spans="1:43">
+      <c r="AT1">
+        <v>0.05</v>
+      </c>
+      <c r="AU1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47">
       <c r="A2" s="1">
         <v>0.1</v>
       </c>
@@ -16066,8 +17686,14 @@
       <c r="AQ2">
         <v>1.471861</v>
       </c>
-    </row>
-    <row r="3" spans="1:43">
+      <c r="AT2">
+        <v>0.1</v>
+      </c>
+      <c r="AU2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47">
       <c r="A3" s="1">
         <v>0.15</v>
       </c>
@@ -16104,8 +17730,14 @@
       <c r="AQ3">
         <v>-0.351632</v>
       </c>
-    </row>
-    <row r="4" spans="1:43">
+      <c r="AT3">
+        <v>0.15</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47">
       <c r="A4" s="1">
         <v>0.2</v>
       </c>
@@ -16142,8 +17774,14 @@
       <c r="AQ4">
         <v>1.6146</v>
       </c>
-    </row>
-    <row r="5" spans="1:43">
+      <c r="AT4">
+        <v>0.2</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47">
       <c r="A5" s="1">
         <v>0.25</v>
       </c>
@@ -16180,8 +17818,14 @@
       <c r="AQ5">
         <v>1.106238</v>
       </c>
-    </row>
-    <row r="6" spans="1:43">
+      <c r="AT5">
+        <v>0.25</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47">
       <c r="A6" s="1">
         <v>0.3</v>
       </c>
@@ -16218,8 +17862,14 @@
       <c r="AQ6">
         <v>2.008665</v>
       </c>
-    </row>
-    <row r="7" spans="1:43">
+      <c r="AT6">
+        <v>0.3</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47">
       <c r="A7" s="1">
         <v>0.35</v>
       </c>
@@ -16256,8 +17906,14 @@
       <c r="AQ7">
         <v>2.674639</v>
       </c>
-    </row>
-    <row r="8" spans="1:43">
+      <c r="AT7">
+        <v>0.35</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47">
       <c r="A8" s="1">
         <v>0.4</v>
       </c>
@@ -16294,8 +17950,14 @@
       <c r="AQ8">
         <v>19.856558</v>
       </c>
-    </row>
-    <row r="9" spans="1:43">
+      <c r="AT8">
+        <v>0.4</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47">
       <c r="A9" s="1">
         <v>0.45</v>
       </c>
@@ -16332,8 +17994,14 @@
       <c r="AQ9">
         <v>17.278831</v>
       </c>
-    </row>
-    <row r="10" spans="1:43">
+      <c r="AT9">
+        <v>0.45</v>
+      </c>
+      <c r="AU9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47">
       <c r="A10" s="1">
         <v>0.5</v>
       </c>
@@ -16370,8 +18038,14 @@
       <c r="AQ10">
         <v>21.077339</v>
       </c>
-    </row>
-    <row r="11" spans="1:43">
+      <c r="AT10">
+        <v>0.5</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47">
       <c r="A11" s="1">
         <v>0.55</v>
       </c>
@@ -16408,8 +18082,14 @@
       <c r="AQ11">
         <v>-0.392361</v>
       </c>
-    </row>
-    <row r="12" spans="1:43">
+      <c r="AT11">
+        <v>0.55</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47">
       <c r="A12" s="1">
         <v>0.6</v>
       </c>
@@ -16446,8 +18126,14 @@
       <c r="AQ12">
         <v>17.534317</v>
       </c>
-    </row>
-    <row r="13" spans="1:43">
+      <c r="AT12">
+        <v>0.6</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47">
       <c r="A13" s="1">
         <v>0.65</v>
       </c>
@@ -16484,8 +18170,14 @@
       <c r="AQ13">
         <v>18.934349</v>
       </c>
-    </row>
-    <row r="14" spans="1:43">
+      <c r="AT13">
+        <v>0.65</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47">
       <c r="A14" s="1">
         <v>0.7</v>
       </c>
@@ -16522,8 +18214,14 @@
       <c r="AQ14">
         <v>18.944988</v>
       </c>
-    </row>
-    <row r="15" spans="1:43">
+      <c r="AT14">
+        <v>0.7</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:47">
       <c r="A15" s="1">
         <v>0.75</v>
       </c>
@@ -16560,8 +18258,14 @@
       <c r="AQ15">
         <v>13.76737</v>
       </c>
-    </row>
-    <row r="16" spans="1:43">
+      <c r="AT15">
+        <v>0.75</v>
+      </c>
+      <c r="AU15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:47">
       <c r="A16" s="1">
         <v>0.8</v>
       </c>
@@ -16598,8 +18302,14 @@
       <c r="AQ16">
         <v>21.326647</v>
       </c>
-    </row>
-    <row r="17" spans="1:43">
+      <c r="AT16">
+        <v>0.8</v>
+      </c>
+      <c r="AU16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47">
       <c r="A17" s="1">
         <v>0.85</v>
       </c>
@@ -16636,8 +18346,14 @@
       <c r="AQ17">
         <v>6.442737</v>
       </c>
-    </row>
-    <row r="18" spans="1:43">
+      <c r="AT17">
+        <v>0.85</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47">
       <c r="A18" s="1">
         <v>0.9</v>
       </c>
@@ -16674,8 +18390,14 @@
       <c r="AQ18">
         <v>0.01077</v>
       </c>
-    </row>
-    <row r="19" spans="1:43">
+      <c r="AT18">
+        <v>0.9</v>
+      </c>
+      <c r="AU18">
+        <v>3.536777</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47">
       <c r="A19" s="1">
         <v>0.95</v>
       </c>
@@ -16712,8 +18434,14 @@
       <c r="AQ19">
         <v>-0.916655</v>
       </c>
-    </row>
-    <row r="20" spans="1:43">
+      <c r="AT19">
+        <v>0.95</v>
+      </c>
+      <c r="AU19">
+        <v>11.224612</v>
+      </c>
+    </row>
+    <row r="20" spans="1:47">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -16750,8 +18478,14 @@
       <c r="AQ20">
         <v>22.553317</v>
       </c>
-    </row>
-    <row r="21" spans="1:43">
+      <c r="AT20">
+        <v>1</v>
+      </c>
+      <c r="AU20">
+        <v>14.642255</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47">
       <c r="A21" s="1">
         <v>1.05</v>
       </c>
@@ -16788,8 +18522,14 @@
       <c r="AQ21">
         <v>21.690609</v>
       </c>
-    </row>
-    <row r="22" spans="1:43">
+      <c r="AT21">
+        <v>1.05</v>
+      </c>
+      <c r="AU21">
+        <v>10.458753</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47">
       <c r="A22" s="1">
         <v>1.1</v>
       </c>
@@ -16826,8 +18566,14 @@
       <c r="AQ22">
         <v>1.651048</v>
       </c>
-    </row>
-    <row r="23" spans="1:43">
+      <c r="AT22">
+        <v>1.1</v>
+      </c>
+      <c r="AU22">
+        <v>7.379002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47">
       <c r="A23" s="1">
         <v>1.15</v>
       </c>
@@ -16864,8 +18610,14 @@
       <c r="AQ23">
         <v>22.375922</v>
       </c>
-    </row>
-    <row r="24" spans="1:43">
+      <c r="AT23">
+        <v>1.15</v>
+      </c>
+      <c r="AU23">
+        <v>6.91978</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47">
       <c r="A24" s="1">
         <v>1.2</v>
       </c>
@@ -16902,8 +18654,14 @@
       <c r="AQ24">
         <v>3.905326</v>
       </c>
-    </row>
-    <row r="25" spans="1:43">
+      <c r="AT24">
+        <v>1.2</v>
+      </c>
+      <c r="AU24">
+        <v>3.978874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47">
       <c r="A25" s="1">
         <v>1.25</v>
       </c>
@@ -16940,8 +18698,14 @@
       <c r="AQ25">
         <v>0.594133</v>
       </c>
-    </row>
-    <row r="26" spans="1:43">
+      <c r="AT25">
+        <v>1.25</v>
+      </c>
+      <c r="AU25">
+        <v>4.583662</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47">
       <c r="A26" s="1">
         <v>1.3</v>
       </c>
@@ -16978,8 +18742,14 @@
       <c r="AQ26">
         <v>4.049308</v>
       </c>
-    </row>
-    <row r="27" spans="1:43">
+      <c r="AT26">
+        <v>1.3</v>
+      </c>
+      <c r="AU26">
+        <v>2.081257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:47">
       <c r="A27" s="1">
         <v>1.35</v>
       </c>
@@ -17016,8 +18786,14 @@
       <c r="AQ27">
         <v>0.960658</v>
       </c>
-    </row>
-    <row r="28" spans="1:43">
+      <c r="AT27">
+        <v>1.35</v>
+      </c>
+      <c r="AU27">
+        <v>3.065206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:47">
       <c r="A28" s="1">
         <v>1.4</v>
       </c>
@@ -17054,8 +18830,14 @@
       <c r="AQ28">
         <v>18.53019</v>
       </c>
-    </row>
-    <row r="29" spans="1:43">
+      <c r="AT28">
+        <v>1.4</v>
+      </c>
+      <c r="AU28">
+        <v>1.818914</v>
+      </c>
+    </row>
+    <row r="29" spans="1:47">
       <c r="A29" s="1">
         <v>1.45</v>
       </c>
@@ -17092,8 +18874,14 @@
       <c r="AQ29">
         <v>-2.927286</v>
       </c>
-    </row>
-    <row r="30" spans="1:43">
+      <c r="AT29">
+        <v>1.45</v>
+      </c>
+      <c r="AU29">
+        <v>1.975717</v>
+      </c>
+    </row>
+    <row r="30" spans="1:47">
       <c r="A30" s="1">
         <v>1.5</v>
       </c>
@@ -17130,8 +18918,14 @@
       <c r="AQ30">
         <v>23.058757</v>
       </c>
-    </row>
-    <row r="31" spans="1:43">
+      <c r="AT30">
+        <v>1.5</v>
+      </c>
+      <c r="AU30">
+        <v>1.167136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:47">
       <c r="A31" s="1">
         <v>1.55</v>
       </c>
@@ -17168,8 +18962,14 @@
       <c r="AQ31">
         <v>20.201963</v>
       </c>
-    </row>
-    <row r="32" spans="1:43">
+      <c r="AT31">
+        <v>1.55</v>
+      </c>
+      <c r="AU31">
+        <v>2.772376</v>
+      </c>
+    </row>
+    <row r="32" spans="1:47">
       <c r="A32" s="1">
         <v>1.6</v>
       </c>
@@ -17206,8 +19006,14 @@
       <c r="AQ32">
         <v>1.002016</v>
       </c>
-    </row>
-    <row r="33" spans="1:43">
+      <c r="AT32">
+        <v>1.6</v>
+      </c>
+      <c r="AU32">
+        <v>1.790493</v>
+      </c>
+    </row>
+    <row r="33" spans="1:47">
       <c r="A33" s="1">
         <v>1.65</v>
       </c>
@@ -17244,8 +19050,14 @@
       <c r="AQ33">
         <v>19.664825</v>
       </c>
-    </row>
-    <row r="34" spans="1:43">
+      <c r="AT33">
+        <v>1.65</v>
+      </c>
+      <c r="AU33">
+        <v>2.411439</v>
+      </c>
+    </row>
+    <row r="34" spans="1:47">
       <c r="A34" s="1">
         <v>1.7</v>
       </c>
@@ -17282,8 +19094,14 @@
       <c r="AQ34">
         <v>19.433288</v>
       </c>
-    </row>
-    <row r="35" spans="1:43">
+      <c r="AT34">
+        <v>1.7</v>
+      </c>
+      <c r="AU34">
+        <v>3.089478</v>
+      </c>
+    </row>
+    <row r="35" spans="1:47">
       <c r="A35" s="1">
         <v>1.75</v>
       </c>
@@ -17320,8 +19138,14 @@
       <c r="AQ35">
         <v>17.048692</v>
       </c>
-    </row>
-    <row r="36" spans="1:43">
+      <c r="AT35">
+        <v>1.75</v>
+      </c>
+      <c r="AU35">
+        <v>4.365393</v>
+      </c>
+    </row>
+    <row r="36" spans="1:47">
       <c r="A36" s="1">
         <v>1.8</v>
       </c>
@@ -17358,8 +19182,14 @@
       <c r="AQ36">
         <v>1.424326</v>
       </c>
-    </row>
-    <row r="37" spans="1:43">
+      <c r="AT36">
+        <v>1.8</v>
+      </c>
+      <c r="AU36">
+        <v>4.951487</v>
+      </c>
+    </row>
+    <row r="37" spans="1:47">
       <c r="A37" s="1">
         <v>1.85</v>
       </c>
@@ -17396,8 +19226,14 @@
       <c r="AQ37">
         <v>-2.59588</v>
       </c>
-    </row>
-    <row r="38" spans="1:43">
+      <c r="AT37">
+        <v>1.85</v>
+      </c>
+      <c r="AU37">
+        <v>4.129426</v>
+      </c>
+    </row>
+    <row r="38" spans="1:47">
       <c r="A38" s="1">
         <v>1.9</v>
       </c>
@@ -17434,8 +19270,14 @@
       <c r="AQ38">
         <v>5.404005</v>
       </c>
-    </row>
-    <row r="39" spans="1:43">
+      <c r="AT38">
+        <v>1.9</v>
+      </c>
+      <c r="AU38">
+        <v>5.109711</v>
+      </c>
+    </row>
+    <row r="39" spans="1:47">
       <c r="A39" s="1">
         <v>1.95</v>
       </c>
@@ -17472,8 +19314,14 @@
       <c r="AQ39">
         <v>4.930463</v>
       </c>
-    </row>
-    <row r="40" spans="1:43">
+      <c r="AT39">
+        <v>1.95</v>
+      </c>
+      <c r="AU39">
+        <v>6.611051</v>
+      </c>
+    </row>
+    <row r="40" spans="1:47">
       <c r="A40" s="1">
         <v>2</v>
       </c>
@@ -17510,8 +19358,14 @@
       <c r="AQ40">
         <v>2.847099</v>
       </c>
-    </row>
-    <row r="41" spans="1:43">
+      <c r="AT40">
+        <v>2</v>
+      </c>
+      <c r="AU40">
+        <v>6.92324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:47">
       <c r="A41" s="1">
         <v>2.05</v>
       </c>
@@ -17548,8 +19402,14 @@
       <c r="AQ41">
         <v>1.122495</v>
       </c>
-    </row>
-    <row r="42" spans="1:43">
+      <c r="AT41">
+        <v>2.05</v>
+      </c>
+      <c r="AU41">
+        <v>5.900378</v>
+      </c>
+    </row>
+    <row r="42" spans="1:47">
       <c r="A42" s="1">
         <v>2.1</v>
       </c>
@@ -17586,8 +19446,14 @@
       <c r="AQ42">
         <v>22.400033</v>
       </c>
-    </row>
-    <row r="43" spans="1:43">
+      <c r="AT42">
+        <v>2.1</v>
+      </c>
+      <c r="AU42">
+        <v>6.366198</v>
+      </c>
+    </row>
+    <row r="43" spans="1:47">
       <c r="A43" s="1">
         <v>2.15</v>
       </c>
@@ -17624,8 +19490,14 @@
       <c r="AQ43">
         <v>3.383263</v>
       </c>
-    </row>
-    <row r="44" spans="1:43">
+      <c r="AT43">
+        <v>2.15</v>
+      </c>
+      <c r="AU43">
+        <v>4.441533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:47">
       <c r="A44" s="1">
         <v>2.2</v>
       </c>
@@ -17662,8 +19534,14 @@
       <c r="AQ44">
         <v>-0.051918</v>
       </c>
-    </row>
-    <row r="45" spans="1:43">
+      <c r="AT44">
+        <v>2.2</v>
+      </c>
+      <c r="AU44">
+        <v>4.195903</v>
+      </c>
+    </row>
+    <row r="45" spans="1:47">
       <c r="A45" s="1">
         <v>2.25</v>
       </c>
@@ -17700,8 +19578,14 @@
       <c r="AQ45">
         <v>-1.734718</v>
       </c>
-    </row>
-    <row r="46" spans="1:43">
+      <c r="AT45">
+        <v>2.25</v>
+      </c>
+      <c r="AU45">
+        <v>3.395305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:47">
       <c r="A46" s="1">
         <v>2.3</v>
       </c>
@@ -17738,8 +19622,14 @@
       <c r="AQ46">
         <v>2.855969</v>
       </c>
-    </row>
-    <row r="47" spans="1:43">
+      <c r="AT46">
+        <v>2.3</v>
+      </c>
+      <c r="AU46">
+        <v>4.221066</v>
+      </c>
+    </row>
+    <row r="47" spans="1:47">
       <c r="A47" s="1">
         <v>2.35</v>
       </c>
@@ -17752,6 +19642,9 @@
       <c r="E47">
         <v>0.183165</v>
       </c>
+      <c r="J47" t="s">
+        <v>3</v>
+      </c>
       <c r="N47">
         <v>2.35</v>
       </c>
@@ -17776,8 +19669,14 @@
       <c r="AQ47">
         <v>21.747211</v>
       </c>
-    </row>
-    <row r="48" spans="1:43">
+      <c r="AT47">
+        <v>2.35</v>
+      </c>
+      <c r="AU47">
+        <v>2.844471</v>
+      </c>
+    </row>
+    <row r="48" spans="1:47">
       <c r="A48" s="1">
         <v>2.4</v>
       </c>
@@ -17814,8 +19713,14 @@
       <c r="AQ48">
         <v>1.573776</v>
       </c>
-    </row>
-    <row r="49" spans="1:43">
+      <c r="AT48">
+        <v>2.4</v>
+      </c>
+      <c r="AU48">
+        <v>2.586268</v>
+      </c>
+    </row>
+    <row r="49" spans="1:47">
       <c r="A49" s="1">
         <v>2.45</v>
       </c>
@@ -17852,8 +19757,14 @@
       <c r="AQ49">
         <v>20.346339</v>
       </c>
-    </row>
-    <row r="50" spans="1:43">
+      <c r="AT49">
+        <v>2.45</v>
+      </c>
+      <c r="AU49">
+        <v>3.118138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:47">
       <c r="A50" s="1">
         <v>2.5</v>
       </c>
@@ -17890,8 +19801,14 @@
       <c r="AQ50">
         <v>2.899382</v>
       </c>
-    </row>
-    <row r="51" spans="1:43">
+      <c r="AT50">
+        <v>2.5</v>
+      </c>
+      <c r="AU50">
+        <v>1.973521</v>
+      </c>
+    </row>
+    <row r="51" spans="1:47">
       <c r="A51" s="1">
         <v>2.55</v>
       </c>
@@ -17928,8 +19845,14 @@
       <c r="AQ51">
         <v>-0.041812</v>
       </c>
-    </row>
-    <row r="52" spans="1:43">
+      <c r="AT51">
+        <v>2.55</v>
+      </c>
+      <c r="AU51">
+        <v>3.307926</v>
+      </c>
+    </row>
+    <row r="52" spans="1:47">
       <c r="A52" s="1">
         <v>2.6</v>
       </c>
@@ -17966,8 +19889,14 @@
       <c r="AQ52">
         <v>16.567919</v>
       </c>
-    </row>
-    <row r="53" spans="1:43">
+      <c r="AT52">
+        <v>2.6</v>
+      </c>
+      <c r="AU52">
+        <v>2.754605</v>
+      </c>
+    </row>
+    <row r="53" spans="1:47">
       <c r="A53" s="1">
         <v>2.65</v>
       </c>
@@ -18004,8 +19933,14 @@
       <c r="AQ53">
         <v>12.678571</v>
       </c>
-    </row>
-    <row r="54" spans="1:43">
+      <c r="AT53">
+        <v>2.65</v>
+      </c>
+      <c r="AU53">
+        <v>4.083976</v>
+      </c>
+    </row>
+    <row r="54" spans="1:47">
       <c r="A54" s="1">
         <v>2.7</v>
       </c>
@@ -18042,8 +19977,14 @@
       <c r="AQ54">
         <v>0.097593</v>
       </c>
-    </row>
-    <row r="55" spans="1:43">
+      <c r="AT54">
+        <v>2.7</v>
+      </c>
+      <c r="AU54">
+        <v>4.185186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:47">
       <c r="A55" s="1">
         <v>2.75</v>
       </c>
@@ -18080,8 +20021,14 @@
       <c r="AQ55">
         <v>18.584434</v>
       </c>
-    </row>
-    <row r="56" spans="1:43">
+      <c r="AT55">
+        <v>2.75</v>
+      </c>
+      <c r="AU55">
+        <v>4.745711</v>
+      </c>
+    </row>
+    <row r="56" spans="1:47">
       <c r="A56" s="1">
         <v>2.8</v>
       </c>
@@ -18118,8 +20065,14 @@
       <c r="AQ56">
         <v>2.442763</v>
       </c>
-    </row>
-    <row r="57" spans="1:43">
+      <c r="AT56">
+        <v>2.8</v>
+      </c>
+      <c r="AU56">
+        <v>4.547284</v>
+      </c>
+    </row>
+    <row r="57" spans="1:47">
       <c r="A57" s="1">
         <v>2.85</v>
       </c>
@@ -18156,8 +20109,14 @@
       <c r="AQ57">
         <v>-0.923655</v>
       </c>
-    </row>
-    <row r="58" spans="1:43">
+      <c r="AT57">
+        <v>2.85</v>
+      </c>
+      <c r="AU57">
+        <v>5.249321</v>
+      </c>
+    </row>
+    <row r="58" spans="1:47">
       <c r="A58" s="1">
         <v>2.9</v>
       </c>
@@ -18194,8 +20153,14 @@
       <c r="AQ58">
         <v>19.359268</v>
       </c>
-    </row>
-    <row r="59" spans="1:43">
+      <c r="AT58">
+        <v>2.9</v>
+      </c>
+      <c r="AU58">
+        <v>5.049053</v>
+      </c>
+    </row>
+    <row r="59" spans="1:47">
       <c r="A59" s="1">
         <v>2.95</v>
       </c>
@@ -18232,8 +20197,14 @@
       <c r="AQ59">
         <v>4.172311</v>
       </c>
-    </row>
-    <row r="60" spans="1:43">
+      <c r="AT59">
+        <v>2.95</v>
+      </c>
+      <c r="AU59">
+        <v>5.017427</v>
+      </c>
+    </row>
+    <row r="60" spans="1:47">
       <c r="A60" s="1">
         <v>3</v>
       </c>
@@ -18270,8 +20241,14 @@
       <c r="AQ60">
         <v>6.061411</v>
       </c>
-    </row>
-    <row r="61" spans="1:43">
+      <c r="AT60">
+        <v>3</v>
+      </c>
+      <c r="AU60">
+        <v>4.986855</v>
+      </c>
+    </row>
+    <row r="61" spans="1:47">
       <c r="A61" s="1">
         <v>3.05</v>
       </c>
@@ -18308,8 +20285,14 @@
       <c r="AQ61">
         <v>5.047543</v>
       </c>
-    </row>
-    <row r="62" spans="1:43">
+      <c r="AT61">
+        <v>3.05</v>
+      </c>
+      <c r="AU61">
+        <v>5.583468</v>
+      </c>
+    </row>
+    <row r="62" spans="1:47">
       <c r="A62" s="1">
         <v>3.1</v>
       </c>
@@ -18346,8 +20329,14 @@
       <c r="AQ62">
         <v>3.502227</v>
       </c>
-    </row>
-    <row r="63" spans="1:43">
+      <c r="AT62">
+        <v>3.1</v>
+      </c>
+      <c r="AU62">
+        <v>5.08269</v>
+      </c>
+    </row>
+    <row r="63" spans="1:47">
       <c r="A63" s="1">
         <v>3.15</v>
       </c>
@@ -18384,8 +20373,14 @@
       <c r="AQ63">
         <v>21.634492</v>
       </c>
-    </row>
-    <row r="64" spans="1:43">
+      <c r="AT63">
+        <v>3.15</v>
+      </c>
+      <c r="AU63">
+        <v>4.294657</v>
+      </c>
+    </row>
+    <row r="64" spans="1:47">
       <c r="A64" s="1">
         <v>3.2</v>
       </c>
@@ -18422,8 +20417,14 @@
       <c r="AQ64">
         <v>-0.89406</v>
       </c>
-    </row>
-    <row r="65" spans="1:43">
+      <c r="AT64">
+        <v>3.2</v>
+      </c>
+      <c r="AU64">
+        <v>3.879402</v>
+      </c>
+    </row>
+    <row r="65" spans="1:47">
       <c r="A65" s="1">
         <v>3.25</v>
       </c>
@@ -18460,8 +20461,14 @@
       <c r="AQ65">
         <v>5.590037</v>
       </c>
-    </row>
-    <row r="66" spans="1:43">
+      <c r="AT65">
+        <v>3.25</v>
+      </c>
+      <c r="AU65">
+        <v>3.770748</v>
+      </c>
+    </row>
+    <row r="66" spans="1:47">
       <c r="A66" s="1">
         <v>3.3</v>
       </c>
@@ -18498,8 +20505,14 @@
       <c r="AQ66">
         <v>0.557408</v>
       </c>
-    </row>
-    <row r="67" spans="1:43">
+      <c r="AT66">
+        <v>3.3</v>
+      </c>
+      <c r="AU66">
+        <v>3.279556</v>
+      </c>
+    </row>
+    <row r="67" spans="1:47">
       <c r="A67" s="1">
         <v>3.35</v>
       </c>
@@ -18536,8 +20549,14 @@
       <c r="AQ67">
         <v>3.683978</v>
       </c>
-    </row>
-    <row r="68" spans="1:43">
+      <c r="AT67">
+        <v>3.35</v>
+      </c>
+      <c r="AU67">
+        <v>2.850536</v>
+      </c>
+    </row>
+    <row r="68" spans="1:47">
       <c r="A68" s="1">
         <v>3.4</v>
       </c>
@@ -18574,8 +20593,14 @@
       <c r="AQ68">
         <v>1.762499</v>
       </c>
-    </row>
-    <row r="69" spans="1:43">
+      <c r="AT68">
+        <v>3.4</v>
+      </c>
+      <c r="AU68">
+        <v>2.995858</v>
+      </c>
+    </row>
+    <row r="69" spans="1:47">
       <c r="A69" s="1">
         <v>3.45</v>
       </c>
@@ -18612,8 +20637,14 @@
       <c r="AQ69">
         <v>3.966203</v>
       </c>
-    </row>
-    <row r="70" spans="1:43">
+      <c r="AT69">
+        <v>3.45</v>
+      </c>
+      <c r="AU69">
+        <v>3.552154</v>
+      </c>
+    </row>
+    <row r="70" spans="1:47">
       <c r="A70" s="1">
         <v>3.5</v>
       </c>
@@ -18650,8 +20681,14 @@
       <c r="AQ70">
         <v>-0.796675</v>
       </c>
-    </row>
-    <row r="71" spans="1:43">
+      <c r="AT70">
+        <v>3.5</v>
+      </c>
+      <c r="AU70">
+        <v>4.047083</v>
+      </c>
+    </row>
+    <row r="71" spans="1:47">
       <c r="A71" s="1">
         <v>3.55</v>
       </c>
@@ -18688,8 +20725,14 @@
       <c r="AQ71">
         <v>19.74138</v>
       </c>
-    </row>
-    <row r="72" spans="1:43">
+      <c r="AT71">
+        <v>3.55</v>
+      </c>
+      <c r="AU71">
+        <v>3.721087</v>
+      </c>
+    </row>
+    <row r="72" spans="1:47">
       <c r="A72" s="1">
         <v>3.6</v>
       </c>
@@ -18726,8 +20769,14 @@
       <c r="AQ72">
         <v>21.576128</v>
       </c>
-    </row>
-    <row r="73" spans="1:43">
+      <c r="AT72">
+        <v>3.6</v>
+      </c>
+      <c r="AU72">
+        <v>3.536777</v>
+      </c>
+    </row>
+    <row r="73" spans="1:47">
       <c r="A73" s="1">
         <v>3.65</v>
       </c>
@@ -18764,8 +20813,14 @@
       <c r="AQ73">
         <v>22.133829</v>
       </c>
-    </row>
-    <row r="74" spans="1:43">
+      <c r="AT73">
+        <v>3.65</v>
+      </c>
+      <c r="AU73">
+        <v>4.491222</v>
+      </c>
+    </row>
+    <row r="74" spans="1:47">
       <c r="A74" s="1">
         <v>3.7</v>
       </c>
@@ -18802,8 +20857,14 @@
       <c r="AQ74">
         <v>5.899823</v>
       </c>
-    </row>
-    <row r="75" spans="1:43">
+      <c r="AT74">
+        <v>3.7</v>
+      </c>
+      <c r="AU74">
+        <v>4.860678</v>
+      </c>
+    </row>
+    <row r="75" spans="1:47">
       <c r="A75" s="1">
         <v>3.75</v>
       </c>
@@ -18840,8 +20901,14 @@
       <c r="AQ75">
         <v>1.425711</v>
       </c>
-    </row>
-    <row r="76" spans="1:43">
+      <c r="AT75">
+        <v>3.75</v>
+      </c>
+      <c r="AU75">
+        <v>4.668545</v>
+      </c>
+    </row>
+    <row r="76" spans="1:47">
       <c r="A76" s="1">
         <v>3.8</v>
       </c>
@@ -18878,8 +20945,14 @@
       <c r="AQ76">
         <v>4.471497</v>
       </c>
-    </row>
-    <row r="77" spans="1:43">
+      <c r="AT76">
+        <v>3.8</v>
+      </c>
+      <c r="AU76">
+        <v>4.188288</v>
+      </c>
+    </row>
+    <row r="77" spans="1:47">
       <c r="A77" s="1">
         <v>3.85</v>
       </c>
@@ -18916,8 +20989,14 @@
       <c r="AQ77">
         <v>2.018309</v>
       </c>
-    </row>
-    <row r="78" spans="1:43">
+      <c r="AT77">
+        <v>3.85</v>
+      </c>
+      <c r="AU77">
+        <v>5.622097</v>
+      </c>
+    </row>
+    <row r="78" spans="1:47">
       <c r="A78" s="1">
         <v>3.9</v>
       </c>
@@ -18954,8 +21033,14 @@
       <c r="AQ78">
         <v>9.56933</v>
       </c>
-    </row>
-    <row r="79" spans="1:43">
+      <c r="AT78">
+        <v>3.9</v>
+      </c>
+      <c r="AU78">
+        <v>4.570603</v>
+      </c>
+    </row>
+    <row r="79" spans="1:47">
       <c r="A79" s="1">
         <v>3.95</v>
       </c>
@@ -18992,8 +21077,14 @@
       <c r="AQ79">
         <v>4.067196</v>
       </c>
-    </row>
-    <row r="80" spans="1:43">
+      <c r="AT79">
+        <v>3.95</v>
+      </c>
+      <c r="AU79">
+        <v>4.593333</v>
+      </c>
+    </row>
+    <row r="80" spans="1:47">
       <c r="A80" s="1">
         <v>4</v>
       </c>
@@ -19030,8 +21121,14 @@
       <c r="AQ80">
         <v>5.845403</v>
       </c>
-    </row>
-    <row r="81" spans="1:43">
+      <c r="AT80">
+        <v>4</v>
+      </c>
+      <c r="AU80">
+        <v>4.695071</v>
+      </c>
+    </row>
+    <row r="81" spans="1:47">
       <c r="A81" s="1">
         <v>4.05</v>
       </c>
@@ -19068,8 +21165,14 @@
       <c r="AQ81">
         <v>8.859463</v>
       </c>
-    </row>
-    <row r="82" spans="1:43">
+      <c r="AT81">
+        <v>4.05</v>
+      </c>
+      <c r="AU81">
+        <v>4.519214</v>
+      </c>
+    </row>
+    <row r="82" spans="1:47">
       <c r="A82" s="1">
         <v>4.1</v>
       </c>
@@ -19106,8 +21209,14 @@
       <c r="AQ82">
         <v>8.419417</v>
       </c>
-    </row>
-    <row r="83" spans="1:43">
+      <c r="AT82">
+        <v>4.1</v>
+      </c>
+      <c r="AU82">
+        <v>4.580557</v>
+      </c>
+    </row>
+    <row r="83" spans="1:47">
       <c r="A83" s="1">
         <v>4.15</v>
       </c>
@@ -19144,8 +21253,14 @@
       <c r="AQ83">
         <v>7.016995</v>
       </c>
-    </row>
-    <row r="84" spans="1:43">
+      <c r="AT83">
+        <v>4.15</v>
+      </c>
+      <c r="AU83">
+        <v>3.604955</v>
+      </c>
+    </row>
+    <row r="84" spans="1:47">
       <c r="A84" s="1">
         <v>4.2</v>
       </c>
@@ -19182,8 +21297,14 @@
       <c r="AQ84">
         <v>3.995745</v>
       </c>
-    </row>
-    <row r="85" spans="1:43">
+      <c r="AT84">
+        <v>4.2</v>
+      </c>
+      <c r="AU84">
+        <v>3.562039</v>
+      </c>
+    </row>
+    <row r="85" spans="1:47">
       <c r="A85" s="1">
         <v>4.25</v>
       </c>
@@ -19220,8 +21341,14 @@
       <c r="AQ85">
         <v>6.071659</v>
       </c>
-    </row>
-    <row r="86" spans="1:43">
+      <c r="AT85">
+        <v>4.25</v>
+      </c>
+      <c r="AU85">
+        <v>2.883513</v>
+      </c>
+    </row>
+    <row r="86" spans="1:47">
       <c r="A86" s="1">
         <v>4.3</v>
       </c>
@@ -19258,8 +21385,14 @@
       <c r="AQ86">
         <v>2.697111</v>
       </c>
-    </row>
-    <row r="87" spans="1:43">
+      <c r="AT86">
+        <v>4.3</v>
+      </c>
+      <c r="AU86">
+        <v>3.553227</v>
+      </c>
+    </row>
+    <row r="87" spans="1:47">
       <c r="A87" s="1">
         <v>4.35</v>
       </c>
@@ -19296,8 +21429,14 @@
       <c r="AQ87">
         <v>5.001009</v>
       </c>
-    </row>
-    <row r="88" spans="1:43">
+      <c r="AT87">
+        <v>4.35</v>
+      </c>
+      <c r="AU87">
+        <v>3.841671</v>
+      </c>
+    </row>
+    <row r="88" spans="1:47">
       <c r="A88" s="1">
         <v>4.4</v>
       </c>
@@ -19334,8 +21473,14 @@
       <c r="AQ88">
         <v>-1.165026</v>
       </c>
-    </row>
-    <row r="89" spans="1:43">
+      <c r="AT88">
+        <v>4.4</v>
+      </c>
+      <c r="AU88">
+        <v>4.376761</v>
+      </c>
+    </row>
+    <row r="89" spans="1:47">
       <c r="A89" s="1">
         <v>4.45</v>
       </c>
@@ -19372,8 +21517,14 @@
       <c r="AQ89">
         <v>6.281521</v>
       </c>
-    </row>
-    <row r="90" spans="1:43">
+      <c r="AT89">
+        <v>4.45</v>
+      </c>
+      <c r="AU89">
+        <v>4.005697</v>
+      </c>
+    </row>
+    <row r="90" spans="1:47">
       <c r="A90" s="1">
         <v>4.5</v>
       </c>
@@ -19410,8 +21561,14 @@
       <c r="AQ90">
         <v>1.926604</v>
       </c>
-    </row>
-    <row r="91" spans="1:43">
+      <c r="AT90">
+        <v>4.5</v>
+      </c>
+      <c r="AU90">
+        <v>4.244132</v>
+      </c>
+    </row>
+    <row r="91" spans="1:47">
       <c r="A91" s="1">
         <v>4.55</v>
       </c>
@@ -19448,8 +21605,14 @@
       <c r="AQ91">
         <v>3.001851</v>
       </c>
-    </row>
-    <row r="92" spans="1:43">
+      <c r="AT91">
+        <v>4.55</v>
+      </c>
+      <c r="AU91">
+        <v>3.742765</v>
+      </c>
+    </row>
+    <row r="92" spans="1:47">
       <c r="A92" s="1">
         <v>4.6</v>
       </c>
@@ -19486,8 +21649,14 @@
       <c r="AQ92">
         <v>17.626034</v>
       </c>
-    </row>
-    <row r="93" spans="1:43">
+      <c r="AT92">
+        <v>4.6</v>
+      </c>
+      <c r="AU92">
+        <v>4.947643</v>
+      </c>
+    </row>
+    <row r="93" spans="1:47">
       <c r="A93" s="1">
         <v>4.65</v>
       </c>
@@ -19524,8 +21693,14 @@
       <c r="AQ93">
         <v>1.904803</v>
       </c>
-    </row>
-    <row r="94" spans="1:43">
+      <c r="AT93">
+        <v>4.65</v>
+      </c>
+      <c r="AU93">
+        <v>4.278359</v>
+      </c>
+    </row>
+    <row r="94" spans="1:47">
       <c r="A94" s="1">
         <v>4.7</v>
       </c>
@@ -19562,8 +21737,14 @@
       <c r="AQ94">
         <v>23.009958</v>
       </c>
-    </row>
-    <row r="95" spans="1:43">
+      <c r="AT94">
+        <v>4.7</v>
+      </c>
+      <c r="AU94">
+        <v>4.977825</v>
+      </c>
+    </row>
+    <row r="95" spans="1:47">
       <c r="A95" s="1">
         <v>4.75</v>
       </c>
@@ -19600,8 +21781,14 @@
       <c r="AQ95">
         <v>3.1565</v>
       </c>
-    </row>
-    <row r="96" spans="1:43">
+      <c r="AT95">
+        <v>4.75</v>
+      </c>
+      <c r="AU95">
+        <v>5.327502</v>
+      </c>
+    </row>
+    <row r="96" spans="1:47">
       <c r="A96" s="1">
         <v>4.8</v>
       </c>
@@ -19638,8 +21825,14 @@
       <c r="AQ96">
         <v>0.467366</v>
       </c>
-    </row>
-    <row r="97" spans="1:43">
+      <c r="AT96">
+        <v>4.8</v>
+      </c>
+      <c r="AU96">
+        <v>4.277289</v>
+      </c>
+    </row>
+    <row r="97" spans="1:47">
       <c r="A97" s="1">
         <v>4.85</v>
       </c>
@@ -19676,8 +21869,14 @@
       <c r="AQ97">
         <v>3.535558</v>
       </c>
-    </row>
-    <row r="98" spans="1:43">
+      <c r="AT97">
+        <v>4.85</v>
+      </c>
+      <c r="AU97">
+        <v>4.922318</v>
+      </c>
+    </row>
+    <row r="98" spans="1:47">
       <c r="A98" s="1">
         <v>4.9</v>
       </c>
@@ -19714,8 +21913,14 @@
       <c r="AQ98">
         <v>4.482376</v>
       </c>
-    </row>
-    <row r="99" spans="1:43">
+      <c r="AT98">
+        <v>4.9</v>
+      </c>
+      <c r="AU98">
+        <v>3.865191</v>
+      </c>
+    </row>
+    <row r="99" spans="1:47">
       <c r="A99" s="1">
         <v>4.95</v>
       </c>
@@ -19752,8 +21957,14 @@
       <c r="AQ99">
         <v>7.704439</v>
       </c>
-    </row>
-    <row r="100" spans="1:43">
+      <c r="AT99">
+        <v>4.95</v>
+      </c>
+      <c r="AU99">
+        <v>3.665387</v>
+      </c>
+    </row>
+    <row r="100" spans="1:47">
       <c r="A100" s="1">
         <v>5</v>
       </c>
@@ -19789,6 +22000,12 @@
       </c>
       <c r="AQ100">
         <v>11.773929</v>
+      </c>
+      <c r="AT100">
+        <v>5</v>
+      </c>
+      <c r="AU100">
+        <v>4.456338</v>
       </c>
     </row>
     <row r="101" spans="4:43">
